--- a/10.11-10.23 L&F横ぐし確認/成果物/LF_要件追跡_ヒアリング入力済 1.xlsx
+++ b/10.11-10.23 L&F横ぐし確認/成果物/LF_要件追跡_ヒアリング入力済 1.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sheet1_試験追跡'!$A$1:$J$45</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Sheet2_資材追跡'!$A$1:$I$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Sheet2_資材追跡'!$A$1:$I$38</definedName>
   </definedNames>
   <calcPr calcId="191028" fullCalcOnLoad="1"/>
 </workbook>
@@ -75,7 +75,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -122,6 +122,26 @@
         <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDEDED"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -149,7 +169,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -198,6 +218,27 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -564,7 +605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="3"/>
@@ -596,7 +637,7 @@
         </is>
       </c>
       <c r="B2" s="10">
-        <f>COUNTA(Sheet1_試験追跡!C2:C45)</f>
+        <f>COUNTA(Sheet1_試験追跡!C2:C200)</f>
         <v/>
       </c>
       <c r="C2" s="9" t="inlineStr">
@@ -612,7 +653,7 @@
         </is>
       </c>
       <c r="B3" s="10">
-        <f>COUNTIF(Sheet1_試験追跡!I2:I45,"○")</f>
+        <f>COUNTIF(Sheet1_試験追跡!I2:I200,"○")</f>
         <v/>
       </c>
       <c r="C3" s="9" t="inlineStr">
@@ -628,7 +669,7 @@
         </is>
       </c>
       <c r="B4" s="10">
-        <f>COUNTIF(Sheet1_試験追跡!I2:I45,"×")</f>
+        <f>COUNTIF(Sheet1_試験追跡!I2:I200,"×")</f>
         <v/>
       </c>
       <c r="C4" s="9" t="inlineStr">
@@ -644,7 +685,7 @@
         </is>
       </c>
       <c r="B5" s="10">
-        <f>COUNTIF(Sheet2_資材追跡!H2:H21,"○")</f>
+        <f>COUNTIF(Sheet2_資材追跡!H2:H200,"○")</f>
         <v/>
       </c>
       <c r="C5" s="9" t="inlineStr">
@@ -660,7 +701,7 @@
         </is>
       </c>
       <c r="B6" s="10">
-        <f>COUNTIF(Sheet1_試験追跡!I2:I45,"△")+COUNTIF(Sheet2_資材追跡!H2:H21,"△")</f>
+        <f>COUNTIF(Sheet1_試験追跡!I2:I200,"△")+COUNTIF(Sheet2_資材追跡!H2:H200,"△")</f>
         <v/>
       </c>
       <c r="C6" s="9" t="inlineStr">
@@ -676,7 +717,7 @@
         </is>
       </c>
       <c r="B7" s="10">
-        <f>COUNTA(Sheet1_試験追跡!C2:C45)-COUNTA(Sheet1_試験追跡!I2:I45)</f>
+        <f>COUNTA(Sheet1_試験追跡!C2:C200)-COUNTA(Sheet1_試験追跡!I2:I200)</f>
         <v/>
       </c>
       <c r="C7" s="9" t="inlineStr">
@@ -692,7 +733,7 @@
         </is>
       </c>
       <c r="B8" s="10">
-        <f>COUNTA(Sheet2_資材追跡!C2:C21)-COUNTA(Sheet2_資材追跡!H2:H21)</f>
+        <f>COUNTA(Sheet2_資材追跡!C2:C200)-COUNTA(Sheet2_資材追跡!H2:H200)</f>
         <v/>
       </c>
       <c r="C8" s="9" t="inlineStr">
@@ -709,12 +750,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>93/93 読了</t>
+          <t>5本すべて読了</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SCL_変更機能検証_本人確認。★他のSCLは未着手</t>
+          <t>#1 93/93・#2 33/33・#3 25/25・#4 28/28・#5 73/73</t>
         </is>
       </c>
     </row>
@@ -740,12 +781,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>②</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="inlineStr">
-        <is>
-          <t>『リスク管理部』と『リスク管理部以外』で試験内容が完全に同一。権限差分が未検証</t>
+          <t>②【解消】</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>『リスク管理部』と『リスク管理部以外』の権限差分 → SCL#2 ケース25・30 で検証済。管理メニューが リスク管理部=3つ／それ以外・担当者=パスワード変更のみ</t>
         </is>
       </c>
     </row>
@@ -782,6 +823,186 @@
       <c r="B16" s="20" t="inlineStr">
         <is>
           <t>ヒアリングは L&amp;F管理者（リスク管理部）のみだが、SCL は L&amp;Fプロファイル3種を検証。ヒアリングシートの項目漏れでは</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>⑥</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>SCL は検証ポイントごとに別ファイル。1本だけ見て「漏れ」と判断しない（#1の所見2が#2で解消した実例）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>⑦</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>管理機能は会社をまたいで見える（SCL#2 ケース09「★横浜ユーザも表示される」）。本人確認では分離。意図どおりか要確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>⑧</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>ヒアリングのBC照合設定（英字名称NGE79／電話番号FME100／ID情報FME100／国内住所LSE88）がSCL#1ケース27〜35で未確認。名称・フリガナ・生年月日のみ</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>⑨</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>★強化：2026/06廃止の「警察庁（IB）」が #1 でしか取消されていない。#3（更新対象リスト）#4（該当リスト一覧 ケース05・09）には残存。3本中2本で未反映</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>⑩</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>SCL#3 ケース08「取消」の想定結果が『処理状態が取込済になること』。ケース10（タスク実行）と同一文。取消なら「取込済」にはならないはず。コピペミスの可能性</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>権限マトリクス</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>管理者(ﾘｽｸ管理部)=全部可／管理者(それ以外)=本人確認の判定のみ可／担当者=閲覧のみ。3つのSCLを合わせて確定</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>⑪</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>SCL#4（SOAP）は実施日・結果が空欄に見える。未実施の可能性。結果が無いと「試験結果はヒアシ通りか」を確認できない</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>⑫【解消】</t>
+        </is>
+      </c>
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>SCL#4 のメニュー確認 → ケース21・24・27 にあった。L&amp;F3プロファイルとも「未判定照会（連動）」が表示されないこと</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>⑬</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>L&amp;Fがリアルフィルタリング（連動）を使わないことが、ヒアリング項目に見当たらない。⑤・A-15と同じ拾い漏れパターンの可能性</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>⑭★最重要</t>
+        </is>
+      </c>
+      <c r="B27" s="25" t="inlineStr">
+        <is>
+          <t>SCL#1 のレビュー修正が他のSCLに展開されていない。**7点**：①ユーザ情報ファイル ②警察庁(IB)廃止 ③TaskTarget→TaskTrg ④行内要注意情報 ⑤LF00000004のフリガナ ⑥補助コメントの並び順 ⑦保留実施。②は#3・#4にも未反映。→『SCL間で記述が同期していない』1本の指摘にまとめる</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>⑮</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>SCL#5 の横浜セクション（ケース11・20）がメニューを「リアルフィルタリング」と記載。L&amp;Fセクション（26・46）は「バッチフィルタリング」。同一SCL内で食い違い。#4(SOAP)からのコピペの可能性</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>⑯</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>SCL#5 ケース25 のメニュー一覧（未判定照会/判定済照会/ファイル処理状況照会/検索対象者一覧アップロード）に「判定履歴照会」が無いが、ケース46 で使用している。記載漏れの可能性</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>⑰★</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="inlineStr">
+        <is>
+          <t>SCL#5 ケース58 の補助コメントの並び順がヒアリング(A-07)と不一致。#1 では修正済み。このまま試験すると正しい画面を NG 判定してしまう。**是正必要**</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>⑱</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="inlineStr">
+        <is>
+          <t>A-08／A-09／A-11／A-12 は5本すべてに試験項目が無い。**落とし込み漏れの可能性が高い**。特に A-12 は検証ポイント「本人確認」のSCLにあるべき項目</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>⑲</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
+        <is>
+          <t>バッチフィルタリングだけ「リスク管理部以外」も全4メニュー使える（ケース53）。管理・リスト管理では差があった。機能ごとに権限設計が違うが意図どおりか</t>
         </is>
       </c>
     </row>
@@ -892,12 +1113,17 @@
       <c r="F2" s="12" t="n"/>
       <c r="G2" s="12" t="n"/>
       <c r="H2" s="12" t="n"/>
-      <c r="I2" s="18" t="n"/>
+      <c r="I2" s="17" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
       <c r="J2" s="11" t="inlineStr">
         <is>
-          <t>【未発見】
-SCL_変更機能検証_本人確認（93ケース読了）には該当する試験項目が見当たらない。
-★ SCL は複数あるため、他の SCL を確認するまで「漏れ」と判断しない。</t>
+          <t>【SCL 5本（本人確認93／管理33／リスト管理25／SOAP28／バッチ73）すべて読了 した結果】
+HULFT の連携設定。画面試験ではなく**設定ファイル側で確認する性質**。
+A側（試験）に項目が無いのは妥当な可能性が高い。
+→ B（資材追跡）で HULFT 設定を確認する。</t>
         </is>
       </c>
     </row>
@@ -930,12 +1156,16 @@
       <c r="F3" s="12" t="n"/>
       <c r="G3" s="12" t="n"/>
       <c r="H3" s="12" t="n"/>
-      <c r="I3" s="18" t="n"/>
+      <c r="I3" s="17" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
       <c r="J3" s="11" t="inlineStr">
         <is>
-          <t>【未発見】
-SCL_変更機能検証_本人確認（93ケース読了）には該当する試験項目が見当たらない。
-★ SCL は複数あるため、他の SCL を確認するまで「漏れ」と判断しない。</t>
+          <t>【SCL 5本（本人確認93／管理33／リスト管理25／SOAP28／バッチ73）すべて読了 した結果】
+同上。配信周期「四半期」・連携時刻「12:30:00」は HULFT の設定値。
+→ B（資材追跡）で確認する。</t>
         </is>
       </c>
     </row>
@@ -968,12 +1198,15 @@
       <c r="F4" s="12" t="n"/>
       <c r="G4" s="12" t="n"/>
       <c r="H4" s="12" t="n"/>
-      <c r="I4" s="18" t="n"/>
+      <c r="I4" s="17" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
       <c r="J4" s="11" t="inlineStr">
         <is>
-          <t>【未発見】
-SCL_変更機能検証_本人確認（93ケース読了）には該当する試験項目が見当たらない。
-★ SCL は複数あるため、他の SCL を確認するまで「漏れ」と判断しない。</t>
+          <t>【SCL 5本（本人確認93／管理33／リスト管理25／SOAP28／バッチ73）すべて読了 した結果】
+同上（U2KJX002）。→ B（資材追跡）で確認する。</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1236,10 @@
         <is>
           <t>SCL_変更機能検証_本人確認（93ケース読了）
 横浜側 09・12・17・20
-L&amp;F側 26・39・51・58・62・74・81・85</t>
+L&amp;F側 26・39・51・58・62・74・81・85
+SCL_変更機能検証_SOAP ケース05・09（横浜側／L&amp;F側は未確認）
+SCL_変更機能検証_バッチフィルタリング ケース09・13
+SCL_変更機能検証_バッチフィルタリング ケース18・22（横浜）・29（L&amp;F）</t>
         </is>
       </c>
       <c r="G5" s="12" t="inlineStr">
@@ -1033,7 +1269,24 @@
 L&amp;Fプロファイル3ルートで「出る」。裏表そろっている。
 【追記】5つのプロファイルすべてで確認されている。
 横浜2種で「出ない」、L&amp;F2種で「出る」。
-【追記・93ケース読了】6プロファイルすべてで確認。</t>
+【追記・93ケース読了】6プロファイルすべてで確認。
+【追記・SCL#4（SOAP）】
+SOAP連携（リアルフィルタリング）でも横浜プロファイルの
+該当リスト一覧が確認されている（ケース05・09）。
+★ただし「BファイルC情報は表示されないこと」の記載があるかは
+  画面で切れており未確認。L&amp;Fプロファイル分も未確認。
+★SCL#4 は実施日・結果が空欄に見える（未実施の可能性）。
+【訂正・SCL#4 読了】
+SOAP経路（リアルフィルタリング）は **横浜銀行専用**で、
+L&amp;F の3プロファイルすべてで「未判定照会（連動）」が
+表示されない（ケース21・24・27）。
+→ A-04/A-05 は SOAP経路には適用されない。
+【追記・SCL#5（バッチ）】
+バッチ経路でも横浜側で BファイルC情報 が表示されないことを確認
+（ケース09・13）。
+【追記・SCL#5（バッチ）】バッチ経路でも裏表そろって確認されている。
+  横浜側（18・22）… BファイルC情報 は表示されないこと
+  L&amp;F側（29）    … BファイルC情報 が表示されること</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1315,8 @@
       <c r="F6" s="12" t="inlineStr">
         <is>
           <t>SCL_変更機能検証_本人確認（93ケース読了）
-ケース26・39・51・58・62・74・81・85</t>
+ケース26・39・51・58・62・74・81・85
+SCL_変更機能検証_バッチフィルタリング ケース29</t>
         </is>
       </c>
       <c r="G6" s="12" t="inlineStr">
@@ -1093,7 +1347,13 @@
 LF_ADMIN_RISK_EXC（58・62・74）の両方で確認済み。
 ★ただしケース74 に「DJ OFAC/企業リスト」の記載が無い。
   ケース51・58・62 にはある。SCL の反映漏れの可能性あり（要確認）。
-【追記・93ケース読了】L&amp;F3プロファイル（管理者2種＋担当者）で確認。</t>
+【追記・93ケース読了】L&amp;F3プロファイル（管理者2種＋担当者）で確認。
+【追記・SCL#5（バッチ）】★バッチ経路でも確認されていた。
+ケース29（LF_ADMIN_RISK）の『下記は表示されないこと』に
+  ・財務省（MOF）
+  ・JCIF PEPs（JPI）
+  ・DJ 船舶リスト（DJ_SHIPS）
+→ 本人確認（#1）とバッチ（#5）の両経路で確認済み。</t>
         </is>
       </c>
     </row>
@@ -1122,18 +1382,17 @@
       <c r="F7" s="12" t="n"/>
       <c r="G7" s="12" t="n"/>
       <c r="H7" s="12" t="n"/>
-      <c r="I7" s="18" t="n"/>
+      <c r="I7" s="17" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>【未発見】
-SCL_変更機能検証_本人確認（93ケース読了）には該当する試験項目が見当たらない。
-★ SCL は複数あるため、他の SCL を確認するまで「漏れ」と判断しない。
-※ケース11・19・37・48 に『自部店のみ／他部店は表示されないこと』が
-  あるが、これはデータの表示範囲（部店スコープ）であり、
-  ヒアリングの『リストの使い分けを行わない』とは別件。混同しないこと。
-※プロファイルごとにヒットするリストが違う（A-04/A-05）のは
-  “部店ごとの使い分け”ではなく“会社・プロファイルごとの設定”。
-  この整理で合っているか阿部さんに確認したい。</t>
+          <t>【SCL 5本（本人確認93／管理33／リスト管理25／SOAP28／バッチ73）すべて読了 した結果】
+「使い分けを行わない」＝**ないことの確認**。試験項目にしにくい性質。
+→ B（資材追跡）で 25_部店フィルタリング設定 を見て、
+  全部店が同一設定であることを確認するのが自然。</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1432,8 @@
         <is>
           <t>SCL_変更機能検証_本人確認
 ケース40・63（主）
-ケース43・45・66・68</t>
+ケース43・45・66・68
+SCL_変更機能検証_バッチフィルタリング ケース42・44</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
@@ -1203,14 +1463,24 @@
       </c>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>◎ ヒアリング備考の 1〜6 の並びと完全一致。
+          <t>★不備あり（指摘候補⑰）
+◎ ヒアリング備考の 1〜6 の並びと完全一致。
   1 該当あり（コンプラ先）／2 該当あり（マーク先）／3 該当あり（C情報）
   4 該当あり（その他）／5 該当なし／6 取消し
 表示内容だけでなく**表示順まで**試験項目に落ちている。
 しかも SCL 側で並び順の誤りが修正されており、是正済みの状態。
 【追記】ケース63 で2つ目のL&amp;Fプロファイルでも確認。
 判定実施は 43/45/66/68 の4ケースで
-「チェック有無 × プルダウン／テキスト」の4通りを網羅している。</t>
+「チェック有無 × プルダウン／テキスト」の4通りを網羅している。
+【追記・SCL#5】バッチ経路でも補助コメントの
+プルダウン選択（42）とテキスト入力（44）を確認。
+【追記・SCL#5 ケース58】★重要
+補助コメントの並び順が**ヒアリングと一致していない**。
+  ヒアリング   1 コンプラ先/2 マーク先/**3 C情報**/4 その他/5 該当なし/6 取消し
+  #1 ケース40  上記どおり（並び順修正済）
+  #5 ケース58  コンプラ先/マーク先/その他/該当なし/**C情報**/取消し
+→ #1 の修正が #5 に未反映。このまま試験すると、
+  正しい画面を見て NG と判定してしまう。**是正必要。**</t>
         </is>
       </c>
     </row>
@@ -1260,12 +1530,19 @@
       <c r="F9" s="12" t="n"/>
       <c r="G9" s="12" t="n"/>
       <c r="H9" s="12" t="n"/>
-      <c r="I9" s="18" t="n"/>
+      <c r="I9" s="27" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>【未発見】
-SCL_変更機能検証_本人確認（93ケース読了）には該当する試験項目が見当たらない。
-★ SCL は複数あるため、他の SCL を確認するまで「漏れ」と判断しない。</t>
+          <t>【SCL 5本（本人確認93／管理33／リスト管理25／SOAP28／バッチ73）すべて読了 した結果】
+**5本すべてに該当する試験項目が無い。**
+ファイル記号O〜T のリスト利用設定（OFAC○ MOF× JP× NPA○ …）は
+フィルタリングの挙動に直結するため、試験できるはず。
+特にバッチフィルタリング（#5・73ケース）にあると予想したが無かった。
+→ **落とし込み漏れの可能性が高い。**</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1579,18 @@
       <c r="F10" s="12" t="n"/>
       <c r="G10" s="12" t="n"/>
       <c r="H10" s="12" t="n"/>
-      <c r="I10" s="18" t="n"/>
+      <c r="I10" s="27" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
       <c r="J10" s="11" t="inlineStr">
         <is>
-          <t>【未発見】
-SCL_変更機能検証_本人確認（93ケース読了）には該当する試験項目が見当たらない。
-★ SCL は複数あるため、他の SCL を確認するまで「漏れ」と判断しない。</t>
+          <t>【SCL 5本（本人確認93／管理33／リスト管理25／SOAP28／バッチ73）すべて読了 した結果】
+**5本すべてに該当する試験項目が無い。**
+前回判定適用（BFZ/BFS/DSF/SHF いずれも「有」）は
+判定画面の挙動に直結するため、試験できるはず。
+→ **落とし込み漏れの可能性が高い。**</t>
         </is>
       </c>
     </row>
@@ -1336,12 +1619,17 @@
       <c r="F11" s="12" t="n"/>
       <c r="G11" s="12" t="n"/>
       <c r="H11" s="12" t="n"/>
-      <c r="I11" s="18" t="n"/>
+      <c r="I11" s="17" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
       <c r="J11" s="13" t="inlineStr">
         <is>
-          <t>【未発見】
-SCL_変更機能検証_本人確認（93ケース読了）には該当する試験項目が見当たらない。
-★ SCL は複数あるため、他の SCL を確認するまで「漏れ」と判断しない。</t>
+          <t>【SCL 5本（本人確認93／管理33／リスト管理25／SOAP28／バッチ73）すべて読了 した結果】
+Oculus-monitor への連携。**monitor 側の SCL**にある可能性がある。
+今回確認した5本は filter 側のみ。
+→ monitor 側の試験資料の有無を確認する。</t>
         </is>
       </c>
     </row>
@@ -1379,12 +1667,18 @@
       <c r="F12" s="12" t="n"/>
       <c r="G12" s="12" t="n"/>
       <c r="H12" s="12" t="n"/>
-      <c r="I12" s="18" t="n"/>
+      <c r="I12" s="27" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
       <c r="J12" s="11" t="inlineStr">
         <is>
-          <t>【未発見】
-SCL_変更機能検証_本人確認（93ケース読了）には該当する試験項目が見当たらない。
-★ SCL は複数あるため、他の SCL を確認するまで「漏れ」と判断しない。</t>
+          <t>【SCL 5本（本人確認93／管理33／リスト管理25／SOAP28／バッチ73）すべて読了 した結果】
+**5本すべてに該当する試験項目が無い。**
+ファイル記号O〜T のファイル属性（O：LF-LOANS+ 等）は
+画面表示や処理分岐に影響するため、試験できるはず。
+→ **落とし込み漏れの可能性が高い。**</t>
         </is>
       </c>
     </row>
@@ -1417,16 +1711,19 @@
       <c r="F13" s="12" t="n"/>
       <c r="G13" s="12" t="n"/>
       <c r="H13" s="12" t="n"/>
-      <c r="I13" s="18" t="n"/>
+      <c r="I13" s="27" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
       <c r="J13" s="13" t="inlineStr">
         <is>
-          <t>【未発見】
-SCL_変更機能検証_本人確認（93ケース読了）には該当する試験項目が見当たらない。
-★ SCL は複数あるため、他の SCL を確認するまで「漏れ」と判断しない。
-★この SCL の検証ポイントは「本人確認」なので、
-  A-12『本人確認等で使用するID情報』は本来ここにあるはず。
-  残り42ケースで探す。見つからなければ他の SCL を確認する。
-※ケース40 は『補助コメント』であって『ID情報』ではない。混同しないこと。</t>
+          <t>【SCL 5本（本人確認93／管理33／リスト管理25／SOAP28／バッチ73）すべて読了 した結果】
+★**最も確度が高い落とし込み漏れ。**
+SCL#1 は検証ポイントが「**本人確認**」そのもので93ケースあるが、
+ID情報の表示文字列・表示順を確認する試験項目が無い。
+本来ここにあるべき項目。
+※ケース40・58 は『補助コメント』であって『ID情報』ではない。混同注意。</t>
         </is>
       </c>
     </row>
@@ -1455,7 +1752,9 @@
       <c r="F14" s="12" t="inlineStr">
         <is>
           <t>SCL_変更機能検証_本人確認
-ケース03・26・27〜35</t>
+ケース03・26・27〜35
+SCL_変更機能検証_リスト管理 ケース06・07・09
+SCL_変更機能検証_バッチフィルタリング ケース03・29・30〜36</t>
         </is>
       </c>
       <c r="G14" s="12" t="inlineStr">
@@ -1472,7 +1771,16 @@
     LF00000019 名称／フリガナ
     LF00000020 名称
     LF00000021 名称
-    LF00000025 フリガナ</t>
+    LF00000025 フリガナ
+《SCL_変更機能検証_リスト管理》
+06 更新対象リスト
+  プルダウンに『BファイルC情報』が表示されること
+07・09 ファイルアップロード
+  更新対象リスト＝BファイルC情報／更新種別＝一括 を選び
+  「BファイルC情報.csv」をアップロード
+  → アップロード履歴一覧に「処理中」で追加されること
+10 タスク実行（リストアップロード制御）
+  → 処理状態が「取込済」になること</t>
         </is>
       </c>
       <c r="H14" s="12" t="inlineStr">
@@ -1489,7 +1797,17 @@
         <is>
           <t>◎ 登録・表示・照合の3段階。照合項目（名称・フリガナ・生年月日）の
 組み合わせを9パターンで網羅している。
-※設定値そのもの（マスタSQL・実機DB）は B 側で確認する。</t>
+※設定値そのもの（マスタSQL・実機DB）は B 側で確認する。
+【追記・SCL#3】登録のルートがより詳細に確認されている。
+#1 ケース03 は画面からのアップロードのみだったが、
+#3 では 更新対象リストへの登録 → 一括アップロード →
+タスク実行 → 取込済 まで通しで確認している。
+【追記・SCL#5】バッチ経路でも照合項目を7パターン確認（30〜36）。
+★ただし ケース33（LF00000004）の強調項目が
+  #1 ケース30 と食い違っている。
+    #1  ~~フリガナ~~（赤字取消）／生年月日
+    #5  フリガナ／生年月日
+  → #1 の修正が #5 に未反映（指摘候補⑭の5点目）。</t>
         </is>
       </c>
     </row>
@@ -1517,10 +1835,12 @@
       <c r="E15" s="11" t="n"/>
       <c r="F15" s="12" t="inlineStr">
         <is>
-          <t>SCL_変更機能検証_本人確認（93ケース読了）
-メニュー確認 23・55・78
-権限差分 81・85・86・91・92
-ログイン 22・54・77</t>
+          <t>SCL_変更機能検証_本人確認 ケース23・55・78（メニュー）
+  ケース81・85・91（権限差分）
+SCL_変更機能検証_管理 ケース02（管理メニュー）・07（プロファイル一覧）
+SCL_変更機能検証_リスト管理 ケース02・21・24
+SCL_変更機能検証_SOAP ケース21・24・27
+SCL_変更機能検証_バッチフィルタリング ケース25</t>
         </is>
       </c>
       <c r="G15" s="12" t="inlineStr">
@@ -1531,7 +1851,24 @@
     ・本人確認仕掛照会
     ・判定履歴照会
 47 判定履歴照会 … 実際に遷移でき、一覧画面が表示されること
-22 ログイン／03 リスト登録 … 同ユーザで操作できること</t>
+22 ログイン／03 リスト登録 … 同ユーザで操作できること
+《SCL_変更機能検証_管理》
+02 メニュー確認（LF_ADMIN_RISK）
+  「管理」に パスワード変更／ユーザ管理／操作ログ照会 が表示されること
+07 プロファイル
+  プルダウンに10種（既存7＋L&amp;F3）が表示されること
+25 メニュー確認（LF_ADMIN_RISK_EXC）
+  「管理」に **パスワード変更のみ** が表示されること
+30 メニュー確認（LF_PIC）
+  「管理」に **パスワード変更のみ** が表示されること
+《SCL_変更機能検証_リスト管理》
+02 メニュー確認（LF_ADMIN_RISK）
+  「リスト管理」に 登録済リスト参照／リストアップロード／
+  ホワイトリスト登録 が表示されること
+21 メニュー確認（LF_ADMIN_RISK_EXC）
+  「リスト管理」が表示されていないこと（要文言確認）
+24 メニュー確認（LF_PIC）
+  「リスト管理」が表示されていないこと</t>
         </is>
       </c>
       <c r="H15" s="12" t="inlineStr">
@@ -1574,7 +1911,77 @@
 ★ ヒアリングは A-14『L&amp;F管理者（リスク管理部）の権限』の1件のみだが、
   SCL は L&amp;Fプロファイルを3種類検証している。
   ヒアリングシートに他プロファイルの項目が無いか要確認
-  （Sheet1 の A-15〜A-20 が空欄のため）。</t>
+  （Sheet1 の A-15〜A-20 が空欄のため）。
+【追記・SCL#2（管理）】
+○ ケース02 … 「管理」メニュー（パスワード変更／ユーザ管理／
+   操作ログ照会）が表示されることを確認。
+   → SCL#1 の所見『メニュー確認が本人確認グループのみ』は、
+     管理グループがこの SCL にあったため**一部解消**。
+◎ ケース07 … プロファイルのプルダウンに10種が列挙され、
+   L&amp;Fの3種が明記されている。
+     L&amp;F管理者（リスク管理部）
+     L&amp;F管理者（リスク管理部以外）
+     L&amp;F担当者
+★ ただし『リスク管理部』と『リスク管理部以外』を選んだ時に
+  何が変わるかは、SCL#1・#2 とも未検証のまま。
+★ ヒアリング（A-14）は「L&amp;F管理者（リスク管理部）」の1件のみ。
+  ヒアリングシート2部_プロファイル設定 に3種とも
+  書かれていないか要確認（Sheet1 への拾い漏れの可能性）。
+【追記・SCL#2 読了】★指摘候補②は解消。
+プロファイル別の「管理」メニュー
+                      ﾊﾟｽﾜｰﾄﾞ変更 ﾕｰｻﾞ管理 操作ﾛｸﾞ照会
+  リスク管理部            ○        ○        ○
+  リスク管理部以外        ○        ×        ×
+  担当者                  ○        ×        ×
+→ 権限差分は本人確認ではなく**管理メニュー側**に出る設計だった。
+  SCL#1 だけ見て「差分が未検証」と判断したのは誤りだった。
+L&amp;F 3プロファイルの整理
+                    本人確認 判定 ﾘｽﾄ情報 ﾕｰｻﾞ管理 操作ﾛｸﾞ
+  管理者(ﾘｽｸ管理部)    ○     ○    ○       ○       ○
+  管理者(それ以外)      ○     ○    ○       ×       ×
+  担当者                ○     ×    ×       ×       ×
+【追記・SCL#3（リスト管理）】
+LF_ADMIN_RISK の「リスト管理」メニュー3つを確認（ケース02）。
+→ メニュー確認は 本人確認（#1）／管理（#2）／リスト管理（#3）の
+  3グループすべてで行われている。
+★ ただし #3 で LF_ADMIN_RISK_EXC・LF_PIC の
+  リスト管理メニューを確認しているかは未確認（続きのケース待ち）。
+  ここが分かると権限マトリクスが完成する。
+【追記・SCL#3 読了】★権限マトリクスが完成した。
+メニューグループ別
+                        本人確認  管理      リスト管理
+  管理者(ﾘｽｸ管理部)       ○      ○(3つ)    ○(3つ)
+  管理者(それ以外)         ○      △(1つ)    ×
+  担当者                   ○      △(1つ)    ×
+    管理△＝パスワード変更のみ／○＝ＰＷ変更・ユーザ管理・操作ログ照会
+機能レベル
+                    本人確認 判定 ﾘｽﾄ情報 ﾘｽﾄ管理 ﾕｰｻﾞ管理 操作ﾛｸﾞ
+  管理者(ﾘｽｸ管理部)    ○     ○    ○      ○      ○      ○
+  管理者(それ以外)      ○     ○    ○      ×      ×      ×
+  担当者                ○     ×    ×      ×      ×      ×
+★ SCL#1 で指摘した『EXC がリスト登録できないことの確認が無い』は、
+  SCL#3 ケース21 で確認されていた。→ 解消。
+※ ケース21 の文言は画面右端で切れていたため実ファイルで要確認
+  （ケース構成が ログイン→メニュー確認→ログアウト の3つだけなので
+   「表示されていないこと」とほぼ断定できる）。
+【追記・SCL#4】メニューグループが4つそろった。
+                      本人確認 管理    ﾘｽﾄ管理 ﾘｱﾙﾌｨﾙﾀﾘﾝｸﾞ
+  管理者(ﾘｽｸ管理部)     ○     ○(3)   ○(3)    ×
+  管理者(それ以外)       ○     △(1)   ×       ×
+  担当者                 ○     △(1)   ×       ×
+    管理△＝パスワード変更のみ
+→ L&amp;F は リアルフィルタリング（SOAP連携）を一切使わない。
+【追記・SCL#5】5つ目のメニューグループ「バッチフィルタリング」。
+  未判定照会／判定済照会／ファイル処理状況照会／検索対象者一覧アップロード
+★ケース46 で「バッチフィルタリング－判定履歴照会」を使っているが、
+  ケース25 のメニュー一覧（4つ）に入っていない。記載漏れの可能性。
+【追記・SCL#5 読了】メニューグループが5つそろった。
+                  本人確認 管理   ﾘｽﾄ管理 ﾘｱﾙﾌｨﾙﾀ ﾊﾞｯﾁﾌｨﾙﾀ
+  管理者(ﾘｽｸ管理部) ○     ○(3)  ○(3)   ×      ○(4)
+  管理者(それ以外)   ○     △(1)  ×      ×      ○(4)
+  担当者             ○     △(1)  ×      ×      ×
+★ バッチフィルタリングだけ「リスク管理部以外」も全機能使える。
+  機能ごとに権限設計が違う。意図どおりか確認する価値あり。</t>
         </is>
       </c>
     </row>
@@ -1584,15 +1991,69 @@
           <t>A-15</t>
         </is>
       </c>
-      <c r="B16" s="11" t="n"/>
-      <c r="C16" s="11" t="n"/>
-      <c r="D16" s="11" t="n"/>
-      <c r="E16" s="11" t="n"/>
-      <c r="F16" s="12" t="n"/>
-      <c r="G16" s="12" t="n"/>
-      <c r="H16" s="12" t="n"/>
-      <c r="I16" s="11" t="n"/>
-      <c r="J16" s="11" t="n"/>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>赤枠</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>L&amp;Fの部店コードを LF001〜LF025 の25部店で設定する</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>ヒアリングシート_部店コード</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>2026/04/07追加、2026/05/11 L&amp;F様部店。
+期限：部店数・部店コードは6/19まで、部店名の変更は7/1まで可能。
+マスタ定義：5_部店マスタ／25_部店フィルタリング設定／26_CIFファイルフィルタリング設定</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>SCL_変更機能検証_管理
+ケース06</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>06 所属部店名／LF_ADMIN_RISK
+ユーザ管理画面の「所属部店名」プルダウンを表示する。
+想定結果：下記L&amp;F部店を含んだリストが表示されること
+  一括照合用／監査部／経営企画部／業務改革室／人財部
+  リスク管理部／財務経理部／ITソリューション部
+  営業戦略部／営業推進部／与信企画室
+  融資第一部／融資第二部／債権管理部
+  本店営業第一部／本店営業第二部／本店営業第四部
+  新宿支店／池袋支店／横浜支店／大阪支店／名古屋支店
+  仙台支店／福岡支店／広島営業部</t>
+        </is>
+      </c>
+      <c r="H16" s="12" t="inlineStr">
+        <is>
+          <t>（実施結果はSCL#2のヘッダ未確認）</t>
+        </is>
+      </c>
+      <c r="I16" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="J16" s="11" t="inlineStr">
+        <is>
+          <t>◎ ヒアリングシート_部店コード の LF001〜LF025（25件）と
+  名称・順番とも完全一致。落とし込みができている。
+【新規に識別したヒアリング項目】
+A-01〜A-14 に入っていなかったため追加した項目。
+マスタ定義：5_部店マスタ／25_部店フィルタリング設定／
+            26_CIFファイルフィルタリング設定
+※SCL#2 の実施件数（OK/NG/−）が未確認のため、結果欄は保留。</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
@@ -1607,7 +2068,7 @@
       <c r="F17" s="12" t="n"/>
       <c r="G17" s="12" t="n"/>
       <c r="H17" s="12" t="n"/>
-      <c r="I17" s="11" t="n"/>
+      <c r="I17" s="18" t="n"/>
       <c r="J17" s="11" t="n"/>
     </row>
     <row r="18">
@@ -1623,7 +2084,7 @@
       <c r="F18" s="12" t="n"/>
       <c r="G18" s="12" t="n"/>
       <c r="H18" s="12" t="n"/>
-      <c r="I18" s="11" t="n"/>
+      <c r="I18" s="18" t="n"/>
       <c r="J18" s="11" t="n"/>
     </row>
     <row r="19">
@@ -1639,7 +2100,7 @@
       <c r="F19" s="12" t="n"/>
       <c r="G19" s="12" t="n"/>
       <c r="H19" s="12" t="n"/>
-      <c r="I19" s="11" t="n"/>
+      <c r="I19" s="18" t="n"/>
       <c r="J19" s="11" t="n"/>
     </row>
     <row r="20">
@@ -1655,7 +2116,7 @@
       <c r="F20" s="12" t="n"/>
       <c r="G20" s="12" t="n"/>
       <c r="H20" s="12" t="n"/>
-      <c r="I20" s="11" t="n"/>
+      <c r="I20" s="18" t="n"/>
       <c r="J20" s="11" t="n"/>
     </row>
     <row r="21">
@@ -1671,7 +2132,7 @@
       <c r="F21" s="12" t="n"/>
       <c r="G21" s="12" t="n"/>
       <c r="H21" s="12" t="n"/>
-      <c r="I21" s="11" t="n"/>
+      <c r="I21" s="18" t="n"/>
       <c r="J21" s="11" t="n"/>
     </row>
     <row r="22">
@@ -1683,7 +2144,7 @@
       <c r="F22" s="12" t="n"/>
       <c r="G22" s="12" t="n"/>
       <c r="H22" s="12" t="n"/>
-      <c r="I22" s="11" t="n"/>
+      <c r="I22" s="18" t="n"/>
       <c r="J22" s="11" t="n"/>
     </row>
     <row r="23">
@@ -1695,7 +2156,7 @@
       <c r="F23" s="12" t="n"/>
       <c r="G23" s="12" t="n"/>
       <c r="H23" s="12" t="n"/>
-      <c r="I23" s="11" t="n"/>
+      <c r="I23" s="18" t="n"/>
       <c r="J23" s="11" t="n"/>
     </row>
     <row r="24">
@@ -1707,7 +2168,7 @@
       <c r="F24" s="12" t="n"/>
       <c r="G24" s="12" t="n"/>
       <c r="H24" s="12" t="n"/>
-      <c r="I24" s="11" t="n"/>
+      <c r="I24" s="18" t="n"/>
       <c r="J24" s="11" t="n"/>
     </row>
     <row r="25">
@@ -1719,7 +2180,7 @@
       <c r="F25" s="12" t="n"/>
       <c r="G25" s="12" t="n"/>
       <c r="H25" s="12" t="n"/>
-      <c r="I25" s="11" t="n"/>
+      <c r="I25" s="18" t="n"/>
       <c r="J25" s="11" t="n"/>
     </row>
     <row r="26">
@@ -1731,7 +2192,7 @@
       <c r="F26" s="12" t="n"/>
       <c r="G26" s="12" t="n"/>
       <c r="H26" s="12" t="n"/>
-      <c r="I26" s="11" t="n"/>
+      <c r="I26" s="18" t="n"/>
       <c r="J26" s="11" t="n"/>
     </row>
     <row r="27">
@@ -1743,7 +2204,7 @@
       <c r="F27" s="12" t="n"/>
       <c r="G27" s="12" t="n"/>
       <c r="H27" s="12" t="n"/>
-      <c r="I27" s="11" t="n"/>
+      <c r="I27" s="18" t="n"/>
       <c r="J27" s="11" t="n"/>
     </row>
     <row r="28">
@@ -1755,7 +2216,7 @@
       <c r="F28" s="12" t="n"/>
       <c r="G28" s="12" t="n"/>
       <c r="H28" s="12" t="n"/>
-      <c r="I28" s="11" t="n"/>
+      <c r="I28" s="18" t="n"/>
       <c r="J28" s="11" t="n"/>
     </row>
     <row r="29">
@@ -1767,7 +2228,7 @@
       <c r="F29" s="12" t="n"/>
       <c r="G29" s="12" t="n"/>
       <c r="H29" s="12" t="n"/>
-      <c r="I29" s="11" t="n"/>
+      <c r="I29" s="18" t="n"/>
       <c r="J29" s="11" t="n"/>
     </row>
     <row r="30">
@@ -1779,7 +2240,7 @@
       <c r="F30" s="12" t="n"/>
       <c r="G30" s="12" t="n"/>
       <c r="H30" s="12" t="n"/>
-      <c r="I30" s="11" t="n"/>
+      <c r="I30" s="18" t="n"/>
       <c r="J30" s="11" t="n"/>
     </row>
     <row r="31">
@@ -1791,7 +2252,7 @@
       <c r="F31" s="12" t="n"/>
       <c r="G31" s="12" t="n"/>
       <c r="H31" s="12" t="n"/>
-      <c r="I31" s="11" t="n"/>
+      <c r="I31" s="18" t="n"/>
       <c r="J31" s="11" t="n"/>
     </row>
     <row r="32">
@@ -1803,7 +2264,7 @@
       <c r="F32" s="12" t="n"/>
       <c r="G32" s="12" t="n"/>
       <c r="H32" s="12" t="n"/>
-      <c r="I32" s="11" t="n"/>
+      <c r="I32" s="18" t="n"/>
       <c r="J32" s="11" t="n"/>
     </row>
     <row r="33">
@@ -1815,7 +2276,7 @@
       <c r="F33" s="12" t="n"/>
       <c r="G33" s="12" t="n"/>
       <c r="H33" s="12" t="n"/>
-      <c r="I33" s="11" t="n"/>
+      <c r="I33" s="18" t="n"/>
       <c r="J33" s="11" t="n"/>
     </row>
     <row r="34">
@@ -1827,7 +2288,7 @@
       <c r="F34" s="12" t="n"/>
       <c r="G34" s="12" t="n"/>
       <c r="H34" s="12" t="n"/>
-      <c r="I34" s="11" t="n"/>
+      <c r="I34" s="18" t="n"/>
       <c r="J34" s="11" t="n"/>
     </row>
     <row r="35">
@@ -1839,7 +2300,7 @@
       <c r="F35" s="12" t="n"/>
       <c r="G35" s="12" t="n"/>
       <c r="H35" s="12" t="n"/>
-      <c r="I35" s="11" t="n"/>
+      <c r="I35" s="18" t="n"/>
       <c r="J35" s="11" t="n"/>
     </row>
     <row r="36">
@@ -1851,7 +2312,7 @@
       <c r="F36" s="12" t="n"/>
       <c r="G36" s="12" t="n"/>
       <c r="H36" s="12" t="n"/>
-      <c r="I36" s="11" t="n"/>
+      <c r="I36" s="18" t="n"/>
       <c r="J36" s="11" t="n"/>
     </row>
     <row r="37">
@@ -1863,7 +2324,7 @@
       <c r="F37" s="12" t="n"/>
       <c r="G37" s="12" t="n"/>
       <c r="H37" s="12" t="n"/>
-      <c r="I37" s="11" t="n"/>
+      <c r="I37" s="18" t="n"/>
       <c r="J37" s="11" t="n"/>
     </row>
     <row r="38">
@@ -1875,7 +2336,7 @@
       <c r="F38" s="12" t="n"/>
       <c r="G38" s="12" t="n"/>
       <c r="H38" s="12" t="n"/>
-      <c r="I38" s="11" t="n"/>
+      <c r="I38" s="18" t="n"/>
       <c r="J38" s="11" t="n"/>
     </row>
     <row r="39">
@@ -1887,7 +2348,7 @@
       <c r="F39" s="12" t="n"/>
       <c r="G39" s="12" t="n"/>
       <c r="H39" s="12" t="n"/>
-      <c r="I39" s="11" t="n"/>
+      <c r="I39" s="18" t="n"/>
       <c r="J39" s="11" t="n"/>
     </row>
     <row r="40">
@@ -1899,7 +2360,7 @@
       <c r="F40" s="12" t="n"/>
       <c r="G40" s="12" t="n"/>
       <c r="H40" s="12" t="n"/>
-      <c r="I40" s="11" t="n"/>
+      <c r="I40" s="18" t="n"/>
       <c r="J40" s="11" t="n"/>
     </row>
     <row r="41">
@@ -1911,7 +2372,7 @@
       <c r="F41" s="12" t="n"/>
       <c r="G41" s="12" t="n"/>
       <c r="H41" s="12" t="n"/>
-      <c r="I41" s="11" t="n"/>
+      <c r="I41" s="18" t="n"/>
       <c r="J41" s="11" t="n"/>
     </row>
     <row r="42">
@@ -1923,7 +2384,7 @@
       <c r="F42" s="12" t="n"/>
       <c r="G42" s="12" t="n"/>
       <c r="H42" s="12" t="n"/>
-      <c r="I42" s="11" t="n"/>
+      <c r="I42" s="18" t="n"/>
       <c r="J42" s="11" t="n"/>
     </row>
     <row r="43">
@@ -1935,7 +2396,7 @@
       <c r="F43" s="12" t="n"/>
       <c r="G43" s="12" t="n"/>
       <c r="H43" s="12" t="n"/>
-      <c r="I43" s="11" t="n"/>
+      <c r="I43" s="18" t="n"/>
       <c r="J43" s="11" t="n"/>
     </row>
     <row r="44">
@@ -1947,7 +2408,7 @@
       <c r="F44" s="12" t="n"/>
       <c r="G44" s="12" t="n"/>
       <c r="H44" s="12" t="n"/>
-      <c r="I44" s="11" t="n"/>
+      <c r="I44" s="18" t="n"/>
       <c r="J44" s="11" t="n"/>
     </row>
     <row r="45">
@@ -1959,7 +2420,7 @@
       <c r="F45" s="12" t="n"/>
       <c r="G45" s="12" t="n"/>
       <c r="H45" s="12" t="n"/>
-      <c r="I45" s="11" t="n"/>
+      <c r="I45" s="18" t="n"/>
       <c r="J45" s="11" t="n"/>
     </row>
   </sheetData>
@@ -1979,7 +2440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="9"/>
@@ -2144,7 +2605,9 @@
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="11" t="inlineStr">
         <is>
-          <t>A-04 と対応（ヒアリングシート2部 3-2-3）</t>
+          <t>A-04 と対応（ヒアリングシート2部 3-2-3）
+★確認先の候補（部店コードシートのマスタ定義より）
+  5_部店マスタ／25_部店フィルタリング設定／26_CIFファイルフィルタリング設定</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2634,9 @@
       <c r="H6" s="12" t="n"/>
       <c r="I6" s="11" t="inlineStr">
         <is>
-          <t>A-05 と対応（ヒアリングシート2部 3-2-3）</t>
+          <t>A-05 と対応（ヒアリングシート2部 3-2-3）
+★確認先の候補（部店コードシートのマスタ定義より）
+  5_部店マスタ／25_部店フィルタリング設定／26_CIFファイルフィルタリング設定</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2664,9 @@
       <c r="I7" s="11" t="inlineStr">
         <is>
           <t>A-06 と対応（ヒアリングシート2部 3-2-3）
-★確認の向きが逆：部店別の設定が【入っていないこと】を確認する</t>
+★確認の向きが逆：部店別の設定が【入っていないこと】を確認する
+★確認先の候補（部店コードシートのマスタ定義より）
+  5_部店マスタ／25_部店フィルタリング設定／26_CIFファイルフィルタリング設定</t>
         </is>
       </c>
     </row>
@@ -2373,7 +2840,7 @@
           <t>赤枠</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t>BFILE_CINFO（BファイルC情報）のリスト基本情報を設定する</t>
         </is>
@@ -2385,24 +2852,27 @@
       <c r="H14" s="12" t="n"/>
       <c r="I14" s="11" t="inlineStr">
         <is>
-          <t>A-13 と対応（ヒアリングシート2部_リスト設定）</t>
+          <t>A-13 と対応（ヒアリングシート2部_フィルタリング設定（オンライン））
+★設定の中身は B-13-01〜B-13-17 に展開した（ヒアリングシート2部_フィルタリング設定（オンライン））。
+  横ぐし確認は細目の行で行う。</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>B-14</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>赤枠</t>
+      <c r="A15" s="22" t="inlineStr">
+        <is>
+          <t>B-13-01</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>リスト項目（照合設定）</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>L&amp;F管理者（リスク管理部）の権限を設定する</t>
+          <t>【BファイルC情報(BC)】フリガナ／別称（フリガナ） → 名称及び別称
+LSE ／ 閾値 88</t>
         </is>
       </c>
       <c r="D15" s="12" t="n"/>
@@ -2412,104 +2882,666 @@
       <c r="H15" s="12" t="n"/>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>A-14 と対応（ヒアリングシート2部_プロファイル設定）</t>
+          <t>ヒアリングシート2部_フィルタリング設定（オンライン） より。B-13 の細目。
+※コメント &lt;20260518 MDLC&gt;「L&amp;F様利用リスト『BファイルC情報』の
+  設定内容を記載ください」期限 6/19 に対する回答欄。</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t>B-15</t>
-        </is>
-      </c>
-      <c r="B16" s="11" t="n"/>
-      <c r="C16" s="11" t="n"/>
+      <c r="A16" s="22" t="inlineStr">
+        <is>
+          <t>B-13-02</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>リスト項目（照合設定）</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>【BファイルC情報(BC)】名称／別称（名称） → 名称及び別称
+LSE ／ 閾値 88</t>
+        </is>
+      </c>
       <c r="D16" s="12" t="n"/>
       <c r="E16" s="12" t="n"/>
       <c r="F16" s="12" t="n"/>
       <c r="G16" s="12" t="n"/>
       <c r="H16" s="12" t="n"/>
-      <c r="I16" s="11" t="n"/>
+      <c r="I16" s="11" t="inlineStr">
+        <is>
+          <t>ヒアリングシート2部_フィルタリング設定（オンライン） より。B-13 の細目。
+※コメント &lt;20260518 MDLC&gt;「L&amp;F様利用リスト『BファイルC情報』の
+  設定内容を記載ください」期限 6/19 に対する回答欄。</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>B-16</t>
-        </is>
-      </c>
-      <c r="B17" s="11" t="n"/>
-      <c r="C17" s="11" t="n"/>
+      <c r="A17" s="22" t="inlineStr">
+        <is>
+          <t>B-13-03</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>リスト項目（照合設定）</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>【BファイルC情報(BC)】英字名称／別称（英字名称） → 名称及び別称
+NGE ／ 閾値 79</t>
+        </is>
+      </c>
       <c r="D17" s="12" t="n"/>
       <c r="E17" s="12" t="n"/>
       <c r="F17" s="12" t="n"/>
       <c r="G17" s="12" t="n"/>
       <c r="H17" s="12" t="n"/>
-      <c r="I17" s="11" t="n"/>
+      <c r="I17" s="11" t="inlineStr">
+        <is>
+          <t>ヒアリングシート2部_フィルタリング設定（オンライン） より。B-13 の細目。
+※コメント &lt;20260518 MDLC&gt;「L&amp;F様利用リスト『BファイルC情報』の
+  設定内容を記載ください」期限 6/19 に対する回答欄。</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="inlineStr">
-        <is>
-          <t>B-17</t>
-        </is>
-      </c>
-      <c r="B18" s="11" t="n"/>
-      <c r="C18" s="11" t="n"/>
+      <c r="A18" s="22" t="inlineStr">
+        <is>
+          <t>B-13-04</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>リスト項目（照合設定）</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>【BファイルC情報(BC)】電話番号 → その他ID情報
+FME ／ 閾値 100</t>
+        </is>
+      </c>
       <c r="D18" s="12" t="n"/>
       <c r="E18" s="12" t="n"/>
       <c r="F18" s="12" t="n"/>
       <c r="G18" s="12" t="n"/>
       <c r="H18" s="12" t="n"/>
-      <c r="I18" s="11" t="n"/>
+      <c r="I18" s="11" t="inlineStr">
+        <is>
+          <t>ヒアリングシート2部_フィルタリング設定（オンライン） より。B-13 の細目。
+※コメント &lt;20260518 MDLC&gt;「L&amp;F様利用リスト『BファイルC情報』の
+  設定内容を記載ください」期限 6/19 に対する回答欄。</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>B-18</t>
-        </is>
-      </c>
-      <c r="B19" s="11" t="n"/>
-      <c r="C19" s="11" t="n"/>
+      <c r="A19" s="22" t="inlineStr">
+        <is>
+          <t>B-13-05</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>リスト項目（照合設定）</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>【BファイルC情報(BC)】ID情報／ID情報2 → ID情報
+FME ／ 閾値 100</t>
+        </is>
+      </c>
       <c r="D19" s="12" t="n"/>
       <c r="E19" s="12" t="n"/>
       <c r="F19" s="12" t="n"/>
       <c r="G19" s="12" t="n"/>
       <c r="H19" s="12" t="n"/>
-      <c r="I19" s="11" t="n"/>
+      <c r="I19" s="11" t="inlineStr">
+        <is>
+          <t>ヒアリングシート2部_フィルタリング設定（オンライン） より。B-13 の細目。
+※コメント &lt;20260518 MDLC&gt;「L&amp;F様利用リスト『BファイルC情報』の
+  設定内容を記載ください」期限 6/19 に対する回答欄。</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t>B-19</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="n"/>
-      <c r="C20" s="11" t="n"/>
+      <c r="A20" s="22" t="inlineStr">
+        <is>
+          <t>B-13-06</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>リスト項目（照合設定）</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>【BファイルC情報(BC)】ID情報／ID情報2 → パスポート番号
+FME ／ 閾値 100</t>
+        </is>
+      </c>
       <c r="D20" s="12" t="n"/>
       <c r="E20" s="12" t="n"/>
       <c r="F20" s="12" t="n"/>
       <c r="G20" s="12" t="n"/>
       <c r="H20" s="12" t="n"/>
-      <c r="I20" s="11" t="n"/>
+      <c r="I20" s="11" t="inlineStr">
+        <is>
+          <t>ヒアリングシート2部_フィルタリング設定（オンライン） より。B-13 の細目。
+※コメント &lt;20260518 MDLC&gt;「L&amp;F様利用リスト『BファイルC情報』の
+  設定内容を記載ください」期限 6/19 に対する回答欄。</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>B-20</t>
-        </is>
-      </c>
-      <c r="B21" s="11" t="n"/>
-      <c r="C21" s="11" t="n"/>
+      <c r="A21" s="22" t="inlineStr">
+        <is>
+          <t>B-13-07</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>リスト項目（照合設定）</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>【BファイルC情報(BC)】ID情報／ID情報2 → その他ID情報
+FME ／ 閾値 100</t>
+        </is>
+      </c>
       <c r="D21" s="12" t="n"/>
       <c r="E21" s="12" t="n"/>
       <c r="F21" s="12" t="n"/>
       <c r="G21" s="12" t="n"/>
       <c r="H21" s="12" t="n"/>
-      <c r="I21" s="11" t="n"/>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>ヒアリングシート2部_フィルタリング設定（オンライン） より。B-13 の細目。
+※コメント &lt;20260518 MDLC&gt;「L&amp;F様利用リスト『BファイルC情報』の
+  設定内容を記載ください」期限 6/19 に対する回答欄。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="22" t="inlineStr">
+        <is>
+          <t>B-13-08</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>リスト項目（照合設定）</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>【BファイルC情報(BC)】ID情報／ID情報2 → BIC
+FME ／ 閾値 100</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="n"/>
+      <c r="E22" s="12" t="n"/>
+      <c r="F22" s="12" t="n"/>
+      <c r="G22" s="12" t="n"/>
+      <c r="H22" s="12" t="n"/>
+      <c r="I22" s="11" t="inlineStr">
+        <is>
+          <t>ヒアリングシート2部_フィルタリング設定（オンライン） より。B-13 の細目。
+※コメント &lt;20260518 MDLC&gt;「L&amp;F様利用リスト『BファイルC情報』の
+  設定内容を記載ください」期限 6/19 に対する回答欄。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="22" t="inlineStr">
+        <is>
+          <t>B-13-09</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>リスト項目（照合設定）</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>【BファイルC情報(BC)】国内住所 → 住所・都市・国
+LSE ／ 閾値 88</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="n"/>
+      <c r="E23" s="12" t="n"/>
+      <c r="F23" s="12" t="n"/>
+      <c r="G23" s="12" t="n"/>
+      <c r="H23" s="12" t="n"/>
+      <c r="I23" s="11" t="inlineStr">
+        <is>
+          <t>ヒアリングシート2部_フィルタリング設定（オンライン） より。B-13 の細目。
+※コメント &lt;20260518 MDLC&gt;「L&amp;F様利用リスト『BファイルC情報』の
+  設定内容を記載ください」期限 6/19 に対する回答欄。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="22" t="inlineStr">
+        <is>
+          <t>B-13-10</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>リスト項目（照合設定）</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>【BファイルC情報(BC)】国内郵便番号
+設定なし（全項目 −）</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="n"/>
+      <c r="E24" s="12" t="n"/>
+      <c r="F24" s="12" t="n"/>
+      <c r="G24" s="12" t="n"/>
+      <c r="H24" s="12" t="n"/>
+      <c r="I24" s="11" t="inlineStr">
+        <is>
+          <t>ヒアリングシート2部_フィルタリング設定（オンライン） より。B-13 の細目。
+※コメント &lt;20260518 MDLC&gt;「L&amp;F様利用リスト『BファイルC情報』の
+  設定内容を記載ください」期限 6/19 に対する回答欄。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="22" t="inlineStr">
+        <is>
+          <t>B-13-11</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>リスト項目（照合設定）</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>【BファイルC情報(BC)】英文住所
+設定なし（全項目 −）</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="n"/>
+      <c r="E25" s="12" t="n"/>
+      <c r="F25" s="12" t="n"/>
+      <c r="G25" s="12" t="n"/>
+      <c r="H25" s="12" t="n"/>
+      <c r="I25" s="11" t="inlineStr">
+        <is>
+          <t>ヒアリングシート2部_フィルタリング設定（オンライン） より。B-13 の細目。
+※コメント &lt;20260518 MDLC&gt;「L&amp;F様利用リスト『BファイルC情報』の
+  設定内容を記載ください」期限 6/19 に対する回答欄。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="22" t="inlineStr">
+        <is>
+          <t>B-13-12</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>Hit絞り込み（複合AND）</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>【BファイルC情報(BC)】名称＋フリガナ
+○（AND条件）
+※ × の場合は名称とフリガナがそれぞれ OR 条件でヒットする
+※1 除外条件（①②）は取消線で消されている＝選択していない</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="n"/>
+      <c r="E26" s="12" t="n"/>
+      <c r="F26" s="12" t="n"/>
+      <c r="G26" s="12" t="n"/>
+      <c r="H26" s="12" t="n"/>
+      <c r="I26" s="11" t="inlineStr">
+        <is>
+          <t>ヒアリングシート2部_フィルタリング設定（オンライン） より。B-13 の細目。
+※コメント &lt;20260518 MDLC&gt;「L&amp;F様利用リスト『BファイルC情報』の
+  設定内容を記載ください」期限 6/19 に対する回答欄。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="22" t="inlineStr">
+        <is>
+          <t>B-13-13</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>Hit絞り込み（単項目AND）</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>【BファイルC情報(BC)】設立／生年月日
+○</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="n"/>
+      <c r="E27" s="12" t="n"/>
+      <c r="F27" s="12" t="n"/>
+      <c r="G27" s="12" t="n"/>
+      <c r="H27" s="12" t="n"/>
+      <c r="I27" s="11" t="inlineStr">
+        <is>
+          <t>ヒアリングシート2部_フィルタリング設定（オンライン） より。B-13 の細目。
+※コメント &lt;20260518 MDLC&gt;「L&amp;F様利用リスト『BファイルC情報』の
+  設定内容を記載ください」期限 6/19 に対する回答欄。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="22" t="inlineStr">
+        <is>
+          <t>B-13-14</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>Hit絞り込み（単項目AND）</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>【BファイルC情報(BC)】住所
+×</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="n"/>
+      <c r="E28" s="12" t="n"/>
+      <c r="F28" s="12" t="n"/>
+      <c r="G28" s="12" t="n"/>
+      <c r="H28" s="12" t="n"/>
+      <c r="I28" s="11" t="inlineStr">
+        <is>
+          <t>ヒアリングシート2部_フィルタリング設定（オンライン） より。B-13 の細目。
+※コメント &lt;20260518 MDLC&gt;「L&amp;F様利用リスト『BファイルC情報』の
+  設定内容を記載ください」期限 6/19 に対する回答欄。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="22" t="inlineStr">
+        <is>
+          <t>B-13-15</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
+        <is>
+          <t>Hit絞り込み（単項目AND）</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>【BファイルC情報(BC)】国籍
+×</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="n"/>
+      <c r="E29" s="12" t="n"/>
+      <c r="F29" s="12" t="n"/>
+      <c r="G29" s="12" t="n"/>
+      <c r="H29" s="12" t="n"/>
+      <c r="I29" s="11" t="inlineStr">
+        <is>
+          <t>ヒアリングシート2部_フィルタリング設定（オンライン） より。B-13 の細目。
+※コメント &lt;20260518 MDLC&gt;「L&amp;F様利用リスト『BファイルC情報』の
+  設定内容を記載ください」期限 6/19 に対する回答欄。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="22" t="inlineStr">
+        <is>
+          <t>B-13-16</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>Hit絞り込み（単項目AND）</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>【BファイルC情報(BC)】性別
+×</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="n"/>
+      <c r="E30" s="12" t="n"/>
+      <c r="F30" s="12" t="n"/>
+      <c r="G30" s="12" t="n"/>
+      <c r="H30" s="12" t="n"/>
+      <c r="I30" s="11" t="inlineStr">
+        <is>
+          <t>ヒアリングシート2部_フィルタリング設定（オンライン） より。B-13 の細目。
+※コメント &lt;20260518 MDLC&gt;「L&amp;F様利用リスト『BファイルC情報』の
+  設定内容を記載ください」期限 6/19 に対する回答欄。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="22" t="inlineStr">
+        <is>
+          <t>B-13-17</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>Hit絞り込み（単項目AND）</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>【BファイルC情報(BC)】タイプ
+×</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="n"/>
+      <c r="E31" s="12" t="n"/>
+      <c r="F31" s="12" t="n"/>
+      <c r="G31" s="12" t="n"/>
+      <c r="H31" s="12" t="n"/>
+      <c r="I31" s="11" t="inlineStr">
+        <is>
+          <t>ヒアリングシート2部_フィルタリング設定（オンライン） より。B-13 の細目。
+※コメント &lt;20260518 MDLC&gt;「L&amp;F様利用リスト『BファイルC情報』の
+  設定内容を記載ください」期限 6/19 に対する回答欄。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>B-14</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>赤枠</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>L&amp;F管理者（リスク管理部）の権限を設定する</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="n"/>
+      <c r="E32" s="12" t="n"/>
+      <c r="F32" s="12" t="n"/>
+      <c r="G32" s="12" t="n"/>
+      <c r="H32" s="12" t="n"/>
+      <c r="I32" s="11" t="inlineStr">
+        <is>
+          <t>A-14 と対応（ヒアリングシート2部_プロファイル設定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>B-15</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>赤枠</t>
+        </is>
+      </c>
+      <c r="C33" s="23" t="inlineStr">
+        <is>
+          <t>【部店コード】L&amp;Fの部店を LF001〜LF025 の25件で設定する
+LF001  一括照合用               5
+LF002  監査部                 3
+LF003  経営企画部               5
+LF004  業務改革室               5
+LF005  人財部                 3
+LF006  リスク管理部              6
+LF007  財務経理部               5
+LF008  ITソリューション部         10
+LF009  営業戦略部               5
+LF010  営業推進部               5
+LF011  与信企画室               5
+LF012  融資第一部               5
+LF013  融資第二部               5
+LF014  債権管理部               5
+LF015  本店営業第一部             7
+LF016  本店営業第二部             7
+LF017  本店営業第四部             7
+LF018  新宿支店                4
+LF019  池袋支店                4
+LF020  横浜支店                4
+LF021  大阪支店                4
+LF022  名古屋支店               5
+LF023  仙台支店                4
+LF024  福岡支店                4
+LF025  広島営業部               5</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>マスタ定義（ヒアリングシート記載）
+  5_部店マスタ
+  25_部店フィルタリング設定
+  26_CIFファイルフィルタリング設定</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="n"/>
+      <c r="F33" s="12" t="n"/>
+      <c r="G33" s="12" t="n"/>
+      <c r="H33" s="12" t="n"/>
+      <c r="I33" s="11" t="inlineStr">
+        <is>
+          <t>出典：ヒアリングシート_部店コード（2026/05/11 L&amp;F様部店）
+期限：部店数・部店コードは6/19、部店名の変更は7/1まで
+★D列の数値（5/3/6/10/7/4 等）の意味は未確認。
+  ユーザ数か何かと思われる。要確認。
+★この3つのマスタは A-04/A-05/A-06 の確認先にもなる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>B-16</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="n"/>
+      <c r="C34" s="11" t="n"/>
+      <c r="D34" s="12" t="n"/>
+      <c r="E34" s="12" t="n"/>
+      <c r="F34" s="12" t="n"/>
+      <c r="G34" s="12" t="n"/>
+      <c r="H34" s="12" t="n"/>
+      <c r="I34" s="11" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>B-17</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="n"/>
+      <c r="C35" s="11" t="n"/>
+      <c r="D35" s="12" t="n"/>
+      <c r="E35" s="12" t="n"/>
+      <c r="F35" s="12" t="n"/>
+      <c r="G35" s="12" t="n"/>
+      <c r="H35" s="12" t="n"/>
+      <c r="I35" s="11" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>B-18</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="n"/>
+      <c r="C36" s="11" t="n"/>
+      <c r="D36" s="12" t="n"/>
+      <c r="E36" s="12" t="n"/>
+      <c r="F36" s="12" t="n"/>
+      <c r="G36" s="12" t="n"/>
+      <c r="H36" s="12" t="n"/>
+      <c r="I36" s="11" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>B-19</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="n"/>
+      <c r="C37" s="11" t="n"/>
+      <c r="D37" s="12" t="n"/>
+      <c r="E37" s="12" t="n"/>
+      <c r="F37" s="12" t="n"/>
+      <c r="G37" s="12" t="n"/>
+      <c r="H37" s="12" t="n"/>
+      <c r="I37" s="11" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>B-20</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="n"/>
+      <c r="C38" s="11" t="n"/>
+      <c r="D38" s="12" t="n"/>
+      <c r="E38" s="12" t="n"/>
+      <c r="F38" s="12" t="n"/>
+      <c r="G38" s="12" t="n"/>
+      <c r="H38" s="12" t="n"/>
+      <c r="I38" s="11" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I21"/>
-  <dataValidations count="1">
+  <autoFilter ref="A1:I38"/>
+  <dataValidations count="2">
     <dataValidation sqref="H2:H21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"○,△,×,－"</formula1>
+    </dataValidation>
+    <dataValidation sqref="H2:H38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"○,△,×,－"</formula1>
     </dataValidation>
   </dataValidations>
